--- a/CRUDEX/StaticFiles/Assets/CRUDEX_Novissimo.xlsx
+++ b/CRUDEX/StaticFiles/Assets/CRUDEX_Novissimo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CRUDEX-C#\SGSI_CRUDEX\CRUDEX\StaticFiles\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\C#\SGSI_CRUDEX\CRUDEX\StaticFiles\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{047A6277-FE31-4785-9004-620E3228FA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE544E68-8B66-4943-9F9A-91F1CFDB2C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="969" activeTab="3" xr2:uid="{62178005-964C-499D-8BA4-3BC85200C027}"/>
   </bookViews>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2536" uniqueCount="938">
   <si>
     <t>Id</t>
   </si>
@@ -2840,18 +2840,6 @@
     <t>Virtual?</t>
   </si>
   <si>
-    <t>Id da coluna virtual</t>
-  </si>
-  <si>
-    <t>Valor da coluna virtual</t>
-  </si>
-  <si>
-    <t>Id do valor na tabela</t>
-  </si>
-  <si>
-    <t>Id do valor</t>
-  </si>
-  <si>
     <t>Cadastro</t>
   </si>
   <si>
@@ -2888,13 +2876,34 @@
     <t>ValidMask: 9 = numérico; A = alfabético; X = alfanumérico; # = alfanumérico ou especial</t>
   </si>
   <si>
-    <t>IsOnlySQL</t>
-  </si>
-  <si>
     <t>RightValues</t>
   </si>
   <si>
     <t>5;10</t>
+  </si>
+  <si>
+    <t>MySql.Data</t>
+  </si>
+  <si>
+    <t>MC.Sap.Data.SQLAnywhere</t>
+  </si>
+  <si>
+    <t>Informix.Net.Core</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.1.0.1</t>
+  </si>
+  <si>
+    <t>PackageName</t>
+  </si>
+  <si>
+    <t>PackageVersion</t>
+  </si>
+  <si>
+    <t>Oracle.ManagedDataAccess.Client</t>
+  </si>
+  <si>
+    <t>IBM.Data.Db2</t>
   </si>
 </sst>
 </file>
@@ -4675,7 +4684,7 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="F3" t="s">
         <v>476</v>
@@ -4707,10 +4716,10 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="F4" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -4739,7 +4748,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="F5" t="s">
         <v>477</v>
@@ -5701,7 +5710,7 @@
         <v>crudex</v>
       </c>
       <c r="D22" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="E22" t="s">
         <v>470</v>
@@ -6312,7 +6321,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFDFE00-DE64-4A94-9BDE-C20DE7BA3DCF}">
   <sheetPr codeName="planColumns"/>
-  <dimension ref="A1:Q225"/>
+  <dimension ref="A1:Q220"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -10824,7 +10833,7 @@
     </row>
     <row r="84" spans="1:17">
       <c r="A84" s="20">
-        <f t="shared" ref="A84:A225" si="5">ROW(A84)-1</f>
+        <f t="shared" ref="A84:A220" si="5">ROW(A84)-1</f>
         <v>83</v>
       </c>
       <c r="B84" s="21">
@@ -11555,7 +11564,7 @@
         <v>114</v>
       </c>
       <c r="I97" s="20" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="J97" s="20" t="s">
         <v>26</v>
@@ -14249,7 +14258,7 @@
       </c>
       <c r="G147" s="18" t="str" cm="1">
         <f t="array" ref="G147">GetColumnName(C147,IF(B147=B146,G146,""))</f>
-        <v>RightValue</v>
+        <v>RightValues</v>
       </c>
       <c r="H147" s="18" t="s">
         <v>813</v>
@@ -17916,7 +17925,7 @@
         <v>BigInteger</v>
       </c>
       <c r="F215" s="18">
-        <f t="shared" ref="F215:F221" si="27">IF(G215="Id",5,F214+5)</f>
+        <f t="shared" ref="F215:F220" si="27">IF(G215="Id",5,F214+5)</f>
         <v>10</v>
       </c>
       <c r="G215" s="18" t="str" cm="1">
@@ -18217,234 +18226,6 @@
         <v>26</v>
       </c>
       <c r="Q220" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17">
-      <c r="A221" s="20">
-        <f t="shared" si="5"/>
-        <v>220</v>
-      </c>
-      <c r="B221" s="21">
-        <v>35</v>
-      </c>
-      <c r="C221" s="20" t="str" cm="1">
-        <f t="array" ref="C221">GetValue("Tbl",B221,"Alias")</f>
-        <v>Vrt</v>
-      </c>
-      <c r="D221" s="20">
-        <v>1</v>
-      </c>
-      <c r="E221" s="20" t="str" cm="1">
-        <f t="array" ref="E221">GetValue("Dmn",D221,"Name")</f>
-        <v>BigInteger</v>
-      </c>
-      <c r="F221" s="20" t="e">
-        <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G221" s="20" t="e" cm="1">
-        <f t="array" ref="G221">GetColumnName(C221,IF(B221=B220,G220,""))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H221" s="20" t="s">
-        <v>916</v>
-      </c>
-      <c r="I221" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="J221" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="K221" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="L221" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M221" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N221" s="20"/>
-      <c r="O221" s="20"/>
-      <c r="P221" s="20"/>
-      <c r="Q221" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17">
-      <c r="A222" s="20">
-        <f t="shared" si="5"/>
-        <v>221</v>
-      </c>
-      <c r="B222" s="21">
-        <v>35</v>
-      </c>
-      <c r="C222" s="20" t="str" cm="1">
-        <f t="array" ref="C222">GetValue("Tbl",B222,"Alias")</f>
-        <v>Vrt</v>
-      </c>
-      <c r="D222" s="20">
-        <v>1</v>
-      </c>
-      <c r="E222" s="20" t="str" cm="1">
-        <f t="array" ref="E222">GetValue("Dmn",D222,"Name")</f>
-        <v>BigInteger</v>
-      </c>
-      <c r="F222" s="20" t="e">
-        <f t="shared" ref="F222:F224" si="28">IF(G222="Id",5,F221+5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G222" s="20" t="e" cm="1">
-        <f t="array" ref="G222">GetColumnName(C222,IF(B222=B221,G221,""))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H222" s="20" t="s">
-        <v>595</v>
-      </c>
-      <c r="I222" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="J222" s="20"/>
-      <c r="K222" s="20"/>
-      <c r="L222" s="20"/>
-      <c r="M222" s="20"/>
-      <c r="N222" s="20"/>
-      <c r="O222" s="20"/>
-      <c r="P222" s="20"/>
-      <c r="Q222" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:17">
-      <c r="A223" s="20">
-        <f t="shared" si="5"/>
-        <v>222</v>
-      </c>
-      <c r="B223" s="21">
-        <v>35</v>
-      </c>
-      <c r="C223" s="20" t="str" cm="1">
-        <f t="array" ref="C223">GetValue("Tbl",B223,"Alias")</f>
-        <v>Vrt</v>
-      </c>
-      <c r="D223" s="20">
-        <v>1</v>
-      </c>
-      <c r="E223" s="20" t="str" cm="1">
-        <f t="array" ref="E223">GetValue("Dmn",D223,"Name")</f>
-        <v>BigInteger</v>
-      </c>
-      <c r="F223" s="20" t="e">
-        <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G223" s="20" t="e" cm="1">
-        <f t="array" ref="G223">GetColumnName(C223,IF(B223=B222,G222,""))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H223" s="20" t="s">
-        <v>916</v>
-      </c>
-      <c r="I223" s="20" t="s">
-        <v>626</v>
-      </c>
-      <c r="J223" s="20"/>
-      <c r="K223" s="20"/>
-      <c r="L223" s="20"/>
-      <c r="M223" s="20"/>
-      <c r="N223" s="20"/>
-      <c r="O223" s="20"/>
-      <c r="P223" s="20"/>
-      <c r="Q223" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:17">
-      <c r="A224" s="20">
-        <f t="shared" si="5"/>
-        <v>223</v>
-      </c>
-      <c r="B224" s="21">
-        <v>35</v>
-      </c>
-      <c r="C224" s="20" t="str" cm="1">
-        <f t="array" ref="C224">GetValue("Tbl",B224,"Alias")</f>
-        <v>Vrt</v>
-      </c>
-      <c r="D224" s="20">
-        <v>1</v>
-      </c>
-      <c r="E224" s="20" t="str" cm="1">
-        <f t="array" ref="E224">GetValue("Dmn",D224,"Name")</f>
-        <v>BigInteger</v>
-      </c>
-      <c r="F224" s="20" t="e">
-        <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G224" s="20" t="e" cm="1">
-        <f t="array" ref="G224">GetColumnName(C224,IF(B224=B223,G223,""))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H224" s="20" t="s">
-        <v>918</v>
-      </c>
-      <c r="I224" s="20" t="s">
-        <v>919</v>
-      </c>
-      <c r="J224" s="20"/>
-      <c r="K224" s="20"/>
-      <c r="L224" s="20"/>
-      <c r="M224" s="20"/>
-      <c r="N224" s="20"/>
-      <c r="O224" s="20"/>
-      <c r="P224" s="20"/>
-      <c r="Q224" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:17">
-      <c r="A225" s="20">
-        <f t="shared" si="5"/>
-        <v>224</v>
-      </c>
-      <c r="B225" s="21">
-        <v>35</v>
-      </c>
-      <c r="C225" s="20" t="str" cm="1">
-        <f t="array" ref="C225">GetValue("Tbl",B225,"Alias")</f>
-        <v>Vrt</v>
-      </c>
-      <c r="D225" s="20">
-        <v>42</v>
-      </c>
-      <c r="E225" s="20" t="str" cm="1">
-        <f t="array" ref="E225">GetValue("Dmn",D225,"Name")</f>
-        <v>Variant</v>
-      </c>
-      <c r="F225" s="20" t="e">
-        <f t="shared" ref="F225" si="29">IF(G225="Id",5,F224+5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G225" s="20" t="e" cm="1">
-        <f t="array" ref="G225">GetColumnName(C225,IF(B225=B224,G224,""))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H225" s="20" t="s">
-        <v>917</v>
-      </c>
-      <c r="I225" s="20" t="s">
-        <v>842</v>
-      </c>
-      <c r="J225" s="20"/>
-      <c r="K225" s="20"/>
-      <c r="L225" s="20"/>
-      <c r="M225" s="20"/>
-      <c r="N225" s="20"/>
-      <c r="O225" s="20"/>
-      <c r="P225" s="20"/>
-      <c r="Q225" s="20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20649,17 +20430,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B0C2BC-8D90-42DB-A81A-6E5CF4C471F6}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
+    <row r="1" spans="1:4" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20672,11 +20452,8 @@
       <c r="D1" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <f>ROW(A2)-1</f>
         <v>1</v>
@@ -20690,11 +20467,8 @@
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <f>ROW(A3)-1</f>
         <v>2</v>
@@ -20708,11 +20482,8 @@
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <f>ROW(A4)-1</f>
         <v>3</v>
@@ -20726,11 +20497,8 @@
       <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
         <f>ROW(A5)-1</f>
         <v>4</v>
@@ -20744,11 +20512,8 @@
       <c r="D5">
         <v>2</v>
       </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <f t="shared" ref="A6:A15" si="0">ROW(A6)-1</f>
         <v>5</v>
@@ -20762,11 +20527,8 @@
       <c r="D6">
         <v>2</v>
       </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -20780,11 +20542,8 @@
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -20795,11 +20554,8 @@
       <c r="C8" t="s">
         <v>649</v>
       </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -20810,11 +20566,8 @@
       <c r="C9" t="s">
         <v>650</v>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -20828,11 +20581,8 @@
       <c r="D10">
         <v>2</v>
       </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -20846,11 +20596,8 @@
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -20864,11 +20611,8 @@
       <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -20882,11 +20626,8 @@
       <c r="D13">
         <v>3</v>
       </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -20900,11 +20641,8 @@
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -20916,9 +20654,6 @@
         <v>656</v>
       </c>
       <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -21052,7 +20787,7 @@
         <v>Categories</v>
       </c>
       <c r="D2" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
     </row>
   </sheetData>
@@ -21120,7 +20855,7 @@
         <v>629</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>520</v>
@@ -21249,7 +20984,7 @@
         <v/>
       </c>
       <c r="M4" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="N4" s="6" t="s">
         <v>465</v>
@@ -21303,7 +21038,7 @@
         <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="M1" s="23"/>
       <c r="N1" s="24"/>
@@ -21336,7 +21071,7 @@
         <v>Expression 0001</v>
       </c>
       <c r="H2" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -26075,10 +25810,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>84</v>
@@ -26143,10 +25878,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>69</v>
@@ -26378,16 +26113,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74702516-31F6-40D7-ABB9-F4E63E018310}">
   <sheetPr codeName="Planilha16"/>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="40.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -26401,10 +26139,16 @@
         <v>487</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7">
       <c r="A2">
         <f>ROW(A2)-1</f>
         <v>1</v>
@@ -26418,11 +26162,14 @@
       <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2" t="s">
+        <v>481</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <f t="shared" ref="A3:A11" si="0">ROW(A3)-1</f>
         <v>2</v>
@@ -26436,11 +26183,14 @@
       <c r="D3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3" t="s">
+        <v>930</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -26454,11 +26204,14 @@
       <c r="D4" t="b">
         <v>0</v>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -26472,11 +26225,14 @@
       <c r="D5" t="b">
         <v>0</v>
       </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5" t="s">
+        <v>483</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -26490,11 +26246,14 @@
       <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6" t="s">
+        <v>484</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -26508,11 +26267,14 @@
       <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7" t="s">
+        <v>527</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -26526,11 +26288,17 @@
       <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8" t="s">
+        <v>931</v>
+      </c>
+      <c r="F8" t="s">
+        <v>933</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -26544,11 +26312,14 @@
       <c r="D9" t="b">
         <v>0</v>
       </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9" t="s">
+        <v>932</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -26557,16 +26328,19 @@
         <v>272</v>
       </c>
       <c r="C10" s="15" t="s">
+        <v>936</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
         <v>528</v>
       </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -26575,12 +26349,15 @@
         <v>273</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
         <v>529</v>
       </c>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" t="b">
+      <c r="G11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -38904,7 +38681,7 @@
         <v>752</v>
       </c>
       <c r="I4" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="5" spans="1:9">
